--- a/Input Data Tables/Aircraft Codes.xlsx
+++ b/Input Data Tables/Aircraft Codes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/APAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/Research/APAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEA6CB6-9C81-3C43-BC3A-BEEC826AF952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C63D87-B037-3941-A83D-E21DBA20384B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16360" xr2:uid="{2A5AAF6C-0423-E14F-9660-54AE6FF85CED}"/>
+    <workbookView xWindow="-28460" yWindow="2220" windowWidth="27240" windowHeight="16360" xr2:uid="{2A5AAF6C-0423-E14F-9660-54AE6FF85CED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>FAA Aircraft Code</t>
   </si>
@@ -140,13 +140,46 @@
     <t>B787-10</t>
   </si>
   <si>
-    <t>CRJ-500</t>
-  </si>
-  <si>
     <t>E145</t>
   </si>
   <si>
     <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
+  </si>
+  <si>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
+    <t>B737-300</t>
+  </si>
+  <si>
+    <t>B737-400</t>
+  </si>
+  <si>
+    <t>B737-500</t>
+  </si>
+  <si>
+    <t>E135</t>
+  </si>
+  <si>
+    <t>E140</t>
+  </si>
+  <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
   </si>
 </sst>
 </file>
@@ -527,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871D32B3-3B1F-4D41-9FFA-19600C704C95}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
@@ -544,281 +577,369 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>629</v>
+        <v>676</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>673</v>
+        <v>629</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>530</v>
+        <v>677</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>631</v>
+        <v>673</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>678</v>
+        <v>483</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>638</v>
+        <v>491</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>723</v>
+        <v>484</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>724</v>
+        <v>482</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>698</v>
+        <v>530</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>694</v>
+        <v>631</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>722</v>
+        <v>678</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>699</v>
+        <v>638</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>608</v>
+        <v>724</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>612</v>
+        <v>698</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>614</v>
+        <v>694</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>838</v>
+        <v>722</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>634</v>
+        <v>699</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>888</v>
+        <v>721</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>839</v>
+        <v>655</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>622</v>
+        <v>656</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>696</v>
+        <v>616</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>687</v>
+        <v>612</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>339</v>
+        <v>614</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>359</v>
+        <v>838</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>887</v>
+        <v>634</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
+        <v>623</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>626</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>624</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>696</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>687</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>339</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>359</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>887</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>889</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>837</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>627</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
         <v>637</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>26</v>
       </c>
     </row>
